--- a/data/trans_bre/P1432-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1432-Edad-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,77</t>
+          <t>-0,27; 0,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,44</t>
+          <t>-0,67; 0,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,41</t>
+          <t>-0,64; 0,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,04</t>
+          <t>-0,49; 1,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,01; 1,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,25</t>
+          <t>-0,45; 3,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,55</t>
+          <t>0,45; 3,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,14</t>
+          <t>0,44; 3,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 689,5</t>
+          <t>-40,87; 591,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; —</t>
+          <t>-23,15; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,4</t>
+          <t>-3,58; 2,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,93</t>
+          <t>-4,26; 1,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,57</t>
+          <t>-0,2; 3,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,19; 125,3</t>
+          <t>-67,28; 108,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,91; 124,13</t>
+          <t>-74,82; 101,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,55; —</t>
+          <t>-42,3; 1542,88</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 3,51</t>
+          <t>-5,48; 3,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 10,06</t>
+          <t>3,03; 10,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,79</t>
+          <t>-1,83; 5,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-55,73; 77,47</t>
+          <t>-54,37; 78,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>60,77; 1183,8</t>
+          <t>56,25; 1050,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 182,88</t>
+          <t>-31,53; 190,09</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,96</t>
+          <t>-0,19; 0,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,54</t>
+          <t>0,43; 1,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,45</t>
+          <t>0,49; 1,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 112,56</t>
+          <t>-16,74; 103,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,2; 331,94</t>
+          <t>48,08; 338,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,3; 407,44</t>
+          <t>61,86; 371,26</t>
         </is>
       </c>
     </row>
